--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 18/06/2026, 11:48</x:t>
+    <x:t>Conta: 7983962 | 18/06/2026, 13:54</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>7,00%|Renda Fixa</x:t>
+    <x:t>7,25%|Renda Fixa</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 1.010.477,43</x:t>
   </x:si>
   <x:si>
-    <x:t>7,00%|Pós-Fixada</x:t>
+    <x:t>7,20%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>78,9%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 11.391.842,85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78,90%|Pós-Fixada</x:t>
+    <x:t>78,2%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 10.891.231,29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78,10%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>01/06/2026</x:t>
@@ -112,16 +112,16 @@
     <x:t>CDI 0</x:t>
   </x:si>
   <x:si>
-    <x:t>2.502,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.975.274,04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.991.520,28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.987.864,88</x:t>
+    <x:t>2.084,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.478.205,87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.491.737,91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.488.693,20</x:t>
   </x:si>
   <x:si>
     <x:t>08/06/2026</x:t>
@@ -148,25 +148,25 @@
     <x:t>16/07/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>3.882.959,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.785.610,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.790.866,44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.789.683,74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14,0%|Fundos de Investimento</x:t>
+    <x:t>3.882.403,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.784.781,56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.790.037,24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.788.854,71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14,5%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 2.026.275,52</x:t>
   </x:si>
   <x:si>
-    <x:t>14,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>14,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -235,7 +235,7 @@
     <x:t>0,04%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.682,41</x:t>
+    <x:t>R$ 5.683,12</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -265,7 +265,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>5682,41</x:t>
+    <x:t>5683,12</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -873,13 +873,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>14434278.205159</x:v>
+        <x:v>13933667.3575018</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>14428595.795159</x:v>
+        <x:v>13927984.2375018</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>5682.41</x:v>
+        <x:v>5683.12</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 18/06/2026, 13:54</x:t>
+    <x:t>Conta: 7983962 | 23/06/2026, 13:56</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>7,25%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.010.477,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7,20%|Pós-Fixada</x:t>
+    <x:t>8,19%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.011.823,64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,10%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>78,2%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 10.891.231,29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78,10%|Pós-Fixada</x:t>
+    <x:t>75,3%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 9.302.835,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75,30%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>01/06/2026</x:t>
@@ -112,16 +112,16 @@
     <x:t>CDI 0</x:t>
   </x:si>
   <x:si>
-    <x:t>2.084,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.478.205,87</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.491.737,91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.488.693,20</x:t>
+    <x:t>746,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 887.112,08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 893.151,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 891.792,58</x:t>
   </x:si>
   <x:si>
     <x:t>08/06/2026</x:t>
@@ -136,10 +136,10 @@
     <x:t>R$ 2.600.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.609.456,13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.607.328,50</x:t>
+    <x:t>R$ 2.612.953,16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.610.038,70</x:t>
   </x:si>
   <x:si>
     <x:t>16/06/2026</x:t>
@@ -148,25 +148,25 @@
     <x:t>16/07/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>3.882.403,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.784.781,56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.790.037,24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.788.854,71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14,5%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.026.275,52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>3.881.688,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.783.716,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.796.730,42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.793.802,22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,4%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.029.339,10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,40%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -184,10 +184,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>18/06/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.405,39</x:t>
+    <x:t>23/06/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.407,47</x:t>
   </x:si>
   <x:si>
     <x:t>360,59</x:t>
@@ -196,46 +196,46 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 506.771,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 505.464,76</x:t>
+    <x:t>R$ 507.520,67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 506.045,66</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,43</x:t>
+    <x:t>R$ 1,44</x:t>
   </x:si>
   <x:si>
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 506.727,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 505.409,24</x:t>
+    <x:t>R$ 507.525,55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 506.028,01</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 138,08</x:t>
+    <x:t>R$ 138,29</x:t>
   </x:si>
   <x:si>
     <x:t>7.334,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.012.777,26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.010.309,55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,04%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.683,12</x:t>
+    <x:t>R$ 1.014.292,88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.011.484,16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,05%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.684,43</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -265,7 +265,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>5683,12</x:t>
+    <x:t>5684,43</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -873,13 +873,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>13933667.3575018</x:v>
+        <x:v>12349682.186166</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>13927984.2375018</x:v>
+        <x:v>12343997.756166</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>5683.12</x:v>
+        <x:v>5684.43</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 23/06/2026, 13:56</x:t>
+    <x:t>Conta: 7983962 | 24/06/2026, 16:29</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>8,19%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.011.823,64</x:t>
+    <x:t>R$ 1.012.272,78</x:t>
   </x:si>
   <x:si>
     <x:t>8,10%|Pós-Fixada</x:t>
@@ -94,52 +94,34 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>75,3%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 9.302.835,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75,30%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/06/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/07/2026</x:t>
+    <x:t>59,2%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 7.309.199,61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59,10%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/06/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/07/2026</x:t>
   </x:si>
   <x:si>
     <x:t>CDI 0</x:t>
   </x:si>
   <x:si>
-    <x:t>746,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 887.112,08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 893.151,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 891.792,58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/06/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.851,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.600.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.612.953,16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.610.038,70</x:t>
+    <x:t>1.070,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.502.971,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.511.133,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.509.297,09</x:t>
   </x:si>
   <x:si>
     <x:t>16/06/2026</x:t>
@@ -148,25 +130,25 @@
     <x:t>16/07/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>3.881.688,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.783.716,21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.796.730,42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.793.802,22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16,4%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.029.339,10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16,40%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>3.880.849,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.782.466,10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.798.066,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.794.556,04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32,6%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.030.383,62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -184,22 +166,22 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>23/06/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.407,47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>360,59</x:t>
+    <x:t>24/06/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.408,20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.070,72</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 507.520,67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 506.045,66</x:t>
+    <x:t>R$ 1.507.784,78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.506.250,34</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -211,31 +193,31 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 507.525,55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 506.028,01</x:t>
+    <x:t>R$ 507.795,24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 506.237,01</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 138,29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.334,77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.014.292,88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.011.484,16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,05%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.684,43</x:t>
+    <x:t>R$ 138,36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.562,54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.014.803,60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.011.879,96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,01%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 684,64</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -265,7 +247,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>5684,43</x:t>
+    <x:t>684,64</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -813,7 +795,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K29"/>
+  <x:dimension ref="A1:K28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -873,13 +855,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>12349682.186166</x:v>
+        <x:v>12352540.64868</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>12343997.756166</x:v>
+        <x:v>12351856.00868</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>5684.43</x:v>
+        <x:v>684.64</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1120,127 +1102,125 @@
       <x:c r="K15" s="3"/>
     </x:row>
     <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="13"/>
-      <x:c r="B16" s="13" t="s">
+      <x:c r="A16" s="12"/>
+      <x:c r="B16" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C16" s="13"/>
-      <x:c r="D16" s="13" t="s">
+      <x:c r="C16" s="12"/>
+      <x:c r="D16" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E16" s="13" t="s">
+      <x:c r="E16" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F16" s="13" t="s">
+      <x:c r="F16" s="12" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G16" s="13" t="s">
+      <x:c r="G16" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H16" s="13" t="s">
+      <x:c r="H16" s="12" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="I16" s="13" t="s">
+      <x:c r="I16" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="J16" s="13" t="s">
+      <x:c r="J16" s="12" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="K16" s="3"/>
     </x:row>
-    <x:row r="17" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A17" s="12"/>
-      <x:c r="B17" s="12" t="s">
+    <x:row r="17" spans="1:11">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="4"/>
+      <x:c r="C17" s="4"/>
+      <x:c r="D17" s="4"/>
+      <x:c r="E17" s="4"/>
+      <x:c r="F17" s="4"/>
+      <x:c r="G17" s="4"/>
+      <x:c r="H17" s="4"/>
+      <x:c r="I17" s="4"/>
+      <x:c r="J17" s="4"/>
+      <x:c r="K17" s="4"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A18" s="8" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C17" s="12"/>
-      <x:c r="D17" s="12" t="s">
+      <x:c r="B18" s="9"/>
+      <x:c r="C18" s="9"/>
+      <x:c r="D18" s="9"/>
+      <x:c r="E18" s="9"/>
+      <x:c r="F18" s="9"/>
+      <x:c r="G18" s="10" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="E17" s="12" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F17" s="12" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G17" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H17" s="12" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="I17" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J17" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K17" s="3"/>
-    </x:row>
-    <x:row r="18" spans="1:11">
-      <x:c r="A18" s="4"/>
-      <x:c r="B18" s="4"/>
-      <x:c r="C18" s="4"/>
-      <x:c r="D18" s="4"/>
-      <x:c r="E18" s="4"/>
-      <x:c r="F18" s="4"/>
-      <x:c r="G18" s="4"/>
-      <x:c r="H18" s="4"/>
-      <x:c r="I18" s="4"/>
-      <x:c r="J18" s="4"/>
-      <x:c r="K18" s="4"/>
-    </x:row>
-    <x:row r="19" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A19" s="8" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B19" s="9"/>
-      <x:c r="C19" s="9"/>
-      <x:c r="D19" s="9"/>
-      <x:c r="E19" s="9"/>
-      <x:c r="F19" s="9"/>
-      <x:c r="G19" s="10" t="s">
-        <x:v>49</x:v>
-      </x:c>
+      <x:c r="H18" s="3"/>
+      <x:c r="I18" s="3"/>
+      <x:c r="J18" s="3"/>
+      <x:c r="K18" s="3"/>
+    </x:row>
+    <x:row r="19" spans="1:11">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="4"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+      <x:c r="F19" s="4"/>
+      <x:c r="G19" s="4"/>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11">
-      <x:c r="A20" s="4"/>
-      <x:c r="B20" s="4"/>
-      <x:c r="C20" s="4"/>
-      <x:c r="D20" s="4"/>
-      <x:c r="E20" s="4"/>
-      <x:c r="F20" s="4"/>
-      <x:c r="G20" s="4"/>
+    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A20" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D20" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
       <x:c r="J20" s="3"/>
       <x:c r="K20" s="3"/>
     </x:row>
-    <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A21" s="11" t="s">
+    <x:row r="21" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A21" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B21" s="11" t="s">
+      <x:c r="C21" s="13" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="s">
+      <x:c r="D21" s="13" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D21" s="11" t="s">
+      <x:c r="E21" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="E21" s="11" t="s">
+      <x:c r="F21" s="13" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="s">
-        <x:v>17</x:v>
+      <x:c r="G21" s="13" t="s">
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
@@ -1249,10 +1229,10 @@
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
       <x:c r="A22" s="13" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C22" s="13" t="s">
         <x:v>57</x:v>
@@ -1261,13 +1241,13 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="E22" s="13" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F22" s="13" t="s">
+      <x:c r="G22" s="13" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="G22" s="13" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
@@ -1275,170 +1255,143 @@
       <x:c r="K22" s="3"/>
     </x:row>
     <x:row r="23" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A23" s="13" t="s">
+      <x:c r="A23" s="12" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C23" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B23" s="13" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C23" s="13" t="s">
+      <x:c r="D23" s="12" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D23" s="13" t="s">
+      <x:c r="E23" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F23" s="12" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="E23" s="13" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F23" s="13" t="s">
+      <x:c r="G23" s="12" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="G23" s="13" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
       <x:c r="J23" s="3"/>
       <x:c r="K23" s="3"/>
     </x:row>
-    <x:row r="24" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A24" s="12" t="s">
+    <x:row r="24" spans="1:11">
+      <x:c r="A24" s="4"/>
+      <x:c r="B24" s="4"/>
+      <x:c r="C24" s="4"/>
+      <x:c r="D24" s="4"/>
+      <x:c r="E24" s="4"/>
+      <x:c r="F24" s="4"/>
+      <x:c r="G24" s="4"/>
+      <x:c r="H24" s="4"/>
+      <x:c r="I24" s="4"/>
+      <x:c r="J24" s="4"/>
+      <x:c r="K24" s="4"/>
+    </x:row>
+    <x:row r="25" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A25" s="8" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B25" s="9"/>
+      <x:c r="C25" s="9"/>
+      <x:c r="D25" s="9"/>
+      <x:c r="E25" s="9"/>
+      <x:c r="F25" s="9"/>
+      <x:c r="G25" s="9"/>
+      <x:c r="H25" s="9"/>
+      <x:c r="I25" s="9"/>
+      <x:c r="J25" s="9"/>
+      <x:c r="K25" s="10" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B24" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C24" s="12" t="s">
+    </x:row>
+    <x:row r="26" spans="1:11">
+      <x:c r="A26" s="4"/>
+      <x:c r="B26" s="4"/>
+      <x:c r="C26" s="4"/>
+      <x:c r="D26" s="4"/>
+      <x:c r="E26" s="4"/>
+      <x:c r="F26" s="4"/>
+      <x:c r="G26" s="4"/>
+      <x:c r="H26" s="4"/>
+      <x:c r="I26" s="4"/>
+      <x:c r="J26" s="4"/>
+      <x:c r="K26" s="4"/>
+    </x:row>
+    <x:row r="27" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A27" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B27" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D24" s="12" t="s">
+      <x:c r="D27" s="11" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E24" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F24" s="12" t="s">
+      <x:c r="E27" s="11" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G24" s="12" t="s">
+      <x:c r="F27" s="11" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="H24" s="3"/>
-      <x:c r="I24" s="3"/>
-      <x:c r="J24" s="3"/>
-      <x:c r="K24" s="3"/>
-    </x:row>
-    <x:row r="25" spans="1:11">
-      <x:c r="A25" s="4"/>
-      <x:c r="B25" s="4"/>
-      <x:c r="C25" s="4"/>
-      <x:c r="D25" s="4"/>
-      <x:c r="E25" s="4"/>
-      <x:c r="F25" s="4"/>
-      <x:c r="G25" s="4"/>
-      <x:c r="H25" s="4"/>
-      <x:c r="I25" s="4"/>
-      <x:c r="J25" s="4"/>
-      <x:c r="K25" s="4"/>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A26" s="8" t="s">
+      <x:c r="G27" s="11" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B26" s="9"/>
-      <x:c r="C26" s="9"/>
-      <x:c r="D26" s="9"/>
-      <x:c r="E26" s="9"/>
-      <x:c r="F26" s="9"/>
-      <x:c r="G26" s="9"/>
-      <x:c r="H26" s="9"/>
-      <x:c r="I26" s="9"/>
-      <x:c r="J26" s="9"/>
-      <x:c r="K26" s="10" t="s">
+      <x:c r="H27" s="11" t="s">
         <x:v>73</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" spans="1:11">
-      <x:c r="A27" s="4"/>
-      <x:c r="B27" s="4"/>
-      <x:c r="C27" s="4"/>
-      <x:c r="D27" s="4"/>
-      <x:c r="E27" s="4"/>
-      <x:c r="F27" s="4"/>
-      <x:c r="G27" s="4"/>
-      <x:c r="H27" s="4"/>
-      <x:c r="I27" s="4"/>
-      <x:c r="J27" s="4"/>
-      <x:c r="K27" s="4"/>
-    </x:row>
-    <x:row r="28" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A28" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B28" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C28" s="11" t="s">
+      <x:c r="I27" s="11" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D28" s="11" t="s">
+      <x:c r="J27" s="11" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E28" s="11" t="s">
+      <x:c r="K27" s="11" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F28" s="11" t="s">
+    </x:row>
+    <x:row r="28" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A28" s="12" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G28" s="11" t="s">
+      <x:c r="B28" s="12" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="H28" s="11" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="I28" s="11" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="J28" s="11" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K28" s="11" t="s">
-        <x:v>82</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A29" s="12" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B29" s="12" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C29" s="12" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D29" s="12" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E29" s="12" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F29" s="12" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G29" s="12" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H29" s="12" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="I29" s="12" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="J29" s="12" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="K29" s="12" t="s">
-        <x:v>84</x:v>
+      <x:c r="C28" s="12" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E28" s="12" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F28" s="12" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G28" s="12" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H28" s="12" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I28" s="12" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="J28" s="12" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="K28" s="12" t="s">
+        <x:v>78</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1447,8 +1400,8 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A19:F19"/>
-    <x:mergeCell ref="A26:J26"/>
+    <x:mergeCell ref="A18:F18"/>
+    <x:mergeCell ref="A25:J25"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 24/06/2026, 16:29</x:t>
+    <x:t>Conta: 7983962 | 26/06/2026, 17:04</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>8,19%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.012.272,78</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8,10%|Pós-Fixada</x:t>
+    <x:t>8,69%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.013.171,64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,60%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>59,2%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 7.309.199,61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>59,10%|Pós-Fixada</x:t>
+    <x:t>56,7%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 6.614.491,54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56,70%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>08/06/2026</x:t>
@@ -109,19 +109,19 @@
     <x:t>09/07/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>CDI 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.070,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.502.971,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.511.133,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.509.297,09</x:t>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>574,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 806.266,88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 811.369,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 810.221,48</x:t>
   </x:si>
   <x:si>
     <x:t>16/06/2026</x:t>
@@ -130,25 +130,25 @@
     <x:t>16/07/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>3.880.849,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.782.466,10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.798.066,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.794.556,04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32,6%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.030.383,62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>3.880.768,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.782.345,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.803.121,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.798.447,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,6%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.034.511,45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -166,10 +166,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>24/06/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.408,20</x:t>
+    <x:t>26/06/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.409,65</x:t>
   </x:si>
   <x:si>
     <x:t>1.070,72</x:t>
@@ -178,10 +178,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.507.784,78</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.506.250,34</x:t>
+    <x:t>R$ 1.509.342,11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.506.712,85</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -193,31 +193,31 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 507.795,24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 506.237,01</x:t>
+    <x:t>R$ 508.335,45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 506.655,68</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 138,36</x:t>
+    <x:t>R$ 138,49</x:t>
   </x:si>
   <x:si>
     <x:t>14.562,54</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.014.803,60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.011.879,96</x:t>
+    <x:t>R$ 2.016.833,89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.012.727,15</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 684,64</x:t>
+    <x:t>R$ 684,82</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -247,7 +247,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>684,64</x:t>
+    <x:t>684,82</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -855,13 +855,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>12352540.64868</x:v>
+        <x:v>11662859.452508</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>12351856.00868</x:v>
+        <x:v>11662174.632508</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>684.64</x:v>
+        <x:v>684.82</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 26/06/2026, 17:04</x:t>
+    <x:t>Conta: 7983962 | 29/06/2026, 11:43</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>8,69%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.013.171,64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8,60%|Pós-Fixada</x:t>
+    <x:t>10,3%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.013.621,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,20%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,61 +94,40 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>56,7%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 6.614.491,54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>56,70%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/06/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/07/2026</x:t>
+    <x:t>48,8%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.815.317,82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48,80%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/06/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/07/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>574,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 806.266,88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 811.369,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 810.221,48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/06/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.880.768,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.782.345,41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.803.121,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.798.447,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34,6%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.034.511,45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>3.218.748,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.795.935,42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.810.956,78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,9%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.036.528,33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,90%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -166,10 +145,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>26/06/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.409,65</x:t>
+    <x:t>29/06/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.410,38</x:t>
   </x:si>
   <x:si>
     <x:t>1.070,72</x:t>
@@ -178,10 +157,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.509.342,11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.506.712,85</x:t>
+    <x:t>R$ 1.510.119,79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.507.063,82</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -193,31 +172,31 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 508.335,45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 506.655,68</x:t>
+    <x:t>R$ 508.566,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 506.834,56</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 138,49</x:t>
+    <x:t>R$ 138,56</x:t>
   </x:si>
   <x:si>
     <x:t>14.562,54</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.016.833,89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.012.727,15</x:t>
+    <x:t>R$ 2.017.842,28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.013.264,81</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 684,82</x:t>
+    <x:t>R$ 686,01</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -247,7 +226,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>684,82</x:t>
+    <x:t>686,01</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -795,7 +774,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K28"/>
+  <x:dimension ref="A1:K27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -855,13 +834,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>11662859.452508</x:v>
+        <x:v>9866153.538826</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>11662174.632508</x:v>
+        <x:v>9865467.528826</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>684.82</x:v>
+        <x:v>686.01</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1073,127 +1052,125 @@
       <x:c r="K14" s="3"/>
     </x:row>
     <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="13"/>
-      <x:c r="B15" s="13" t="s">
+      <x:c r="A15" s="12"/>
+      <x:c r="B15" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C15" s="13"/>
-      <x:c r="D15" s="13" t="s">
+      <x:c r="C15" s="12"/>
+      <x:c r="D15" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E15" s="13" t="s">
+      <x:c r="E15" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F15" s="13" t="s">
+      <x:c r="F15" s="12" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G15" s="13" t="s">
+      <x:c r="G15" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H15" s="13" t="s">
+      <x:c r="H15" s="12" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="I15" s="13" t="s">
+      <x:c r="I15" s="12" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="J15" s="13" t="s">
+      <x:c r="K15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="1:11">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="4"/>
+      <x:c r="C16" s="4"/>
+      <x:c r="D16" s="4"/>
+      <x:c r="E16" s="4"/>
+      <x:c r="F16" s="4"/>
+      <x:c r="G16" s="4"/>
+      <x:c r="H16" s="4"/>
+      <x:c r="I16" s="4"/>
+      <x:c r="J16" s="4"/>
+      <x:c r="K16" s="4"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A17" s="8" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="K15" s="3"/>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="12"/>
-      <x:c r="B16" s="12" t="s">
+      <x:c r="B17" s="9"/>
+      <x:c r="C17" s="9"/>
+      <x:c r="D17" s="9"/>
+      <x:c r="E17" s="9"/>
+      <x:c r="F17" s="9"/>
+      <x:c r="G17" s="10" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C16" s="12"/>
-      <x:c r="D16" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E16" s="12" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F16" s="12" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G16" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H16" s="12" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I16" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="J16" s="12" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K16" s="3"/>
-    </x:row>
-    <x:row r="17" spans="1:11">
-      <x:c r="A17" s="4"/>
-      <x:c r="B17" s="4"/>
-      <x:c r="C17" s="4"/>
-      <x:c r="D17" s="4"/>
-      <x:c r="E17" s="4"/>
-      <x:c r="F17" s="4"/>
-      <x:c r="G17" s="4"/>
-      <x:c r="H17" s="4"/>
-      <x:c r="I17" s="4"/>
-      <x:c r="J17" s="4"/>
-      <x:c r="K17" s="4"/>
-    </x:row>
-    <x:row r="18" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A18" s="8" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B18" s="9"/>
-      <x:c r="C18" s="9"/>
-      <x:c r="D18" s="9"/>
-      <x:c r="E18" s="9"/>
-      <x:c r="F18" s="9"/>
-      <x:c r="G18" s="10" t="s">
-        <x:v>43</x:v>
-      </x:c>
+      <x:c r="H17" s="3"/>
+      <x:c r="I17" s="3"/>
+      <x:c r="J17" s="3"/>
+      <x:c r="K17" s="3"/>
+    </x:row>
+    <x:row r="18" spans="1:11">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="4"/>
+      <x:c r="G18" s="4"/>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
       <x:c r="J18" s="3"/>
       <x:c r="K18" s="3"/>
     </x:row>
-    <x:row r="19" spans="1:11">
-      <x:c r="A19" s="4"/>
-      <x:c r="B19" s="4"/>
-      <x:c r="C19" s="4"/>
-      <x:c r="D19" s="4"/>
-      <x:c r="E19" s="4"/>
-      <x:c r="F19" s="4"/>
-      <x:c r="G19" s="4"/>
+    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A19" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A20" s="11" t="s">
+    <x:row r="20" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A20" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B20" s="11" t="s">
+      <x:c r="D20" s="13" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="s">
+      <x:c r="E20" s="13" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D20" s="11" t="s">
+      <x:c r="F20" s="13" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="s">
+      <x:c r="G20" s="13" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
@@ -1205,22 +1182,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C21" s="13" t="s">
+      <x:c r="D21" s="13" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D21" s="13" t="s">
+      <x:c r="E21" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E21" s="13" t="s">
+      <x:c r="G21" s="13" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="F21" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G21" s="13" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
@@ -1228,170 +1205,143 @@
       <x:c r="K21" s="3"/>
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A22" s="13" t="s">
+      <x:c r="A22" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C22" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B22" s="13" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C22" s="13" t="s">
+      <x:c r="E22" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F22" s="12" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D22" s="13" t="s">
+      <x:c r="G22" s="12" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="E22" s="13" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F22" s="13" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G22" s="13" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
       <x:c r="J22" s="3"/>
       <x:c r="K22" s="3"/>
     </x:row>
-    <x:row r="23" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A23" s="12" t="s">
+    <x:row r="23" spans="1:11">
+      <x:c r="A23" s="4"/>
+      <x:c r="B23" s="4"/>
+      <x:c r="C23" s="4"/>
+      <x:c r="D23" s="4"/>
+      <x:c r="E23" s="4"/>
+      <x:c r="F23" s="4"/>
+      <x:c r="G23" s="4"/>
+      <x:c r="H23" s="4"/>
+      <x:c r="I23" s="4"/>
+      <x:c r="J23" s="4"/>
+      <x:c r="K23" s="4"/>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A24" s="8" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B24" s="9"/>
+      <x:c r="C24" s="9"/>
+      <x:c r="D24" s="9"/>
+      <x:c r="E24" s="9"/>
+      <x:c r="F24" s="9"/>
+      <x:c r="G24" s="9"/>
+      <x:c r="H24" s="9"/>
+      <x:c r="I24" s="9"/>
+      <x:c r="J24" s="9"/>
+      <x:c r="K24" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:11">
+      <x:c r="A25" s="4"/>
+      <x:c r="B25" s="4"/>
+      <x:c r="C25" s="4"/>
+      <x:c r="D25" s="4"/>
+      <x:c r="E25" s="4"/>
+      <x:c r="F25" s="4"/>
+      <x:c r="G25" s="4"/>
+      <x:c r="H25" s="4"/>
+      <x:c r="I25" s="4"/>
+      <x:c r="J25" s="4"/>
+      <x:c r="K25" s="4"/>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A26" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B26" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C26" s="11" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B23" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C23" s="12" t="s">
+      <x:c r="D26" s="11" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D23" s="12" t="s">
+      <x:c r="E26" s="11" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="E23" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F23" s="12" t="s">
+      <x:c r="F26" s="11" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G23" s="12" t="s">
+      <x:c r="G26" s="11" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H23" s="3"/>
-      <x:c r="I23" s="3"/>
-      <x:c r="J23" s="3"/>
-      <x:c r="K23" s="3"/>
-    </x:row>
-    <x:row r="24" spans="1:11">
-      <x:c r="A24" s="4"/>
-      <x:c r="B24" s="4"/>
-      <x:c r="C24" s="4"/>
-      <x:c r="D24" s="4"/>
-      <x:c r="E24" s="4"/>
-      <x:c r="F24" s="4"/>
-      <x:c r="G24" s="4"/>
-      <x:c r="H24" s="4"/>
-      <x:c r="I24" s="4"/>
-      <x:c r="J24" s="4"/>
-      <x:c r="K24" s="4"/>
-    </x:row>
-    <x:row r="25" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A25" s="8" t="s">
+      <x:c r="H26" s="11" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B25" s="9"/>
-      <x:c r="C25" s="9"/>
-      <x:c r="D25" s="9"/>
-      <x:c r="E25" s="9"/>
-      <x:c r="F25" s="9"/>
-      <x:c r="G25" s="9"/>
-      <x:c r="H25" s="9"/>
-      <x:c r="I25" s="9"/>
-      <x:c r="J25" s="9"/>
-      <x:c r="K25" s="10" t="s">
+      <x:c r="I26" s="11" t="s">
         <x:v>67</x:v>
       </x:c>
-    </x:row>
-    <x:row r="26" spans="1:11">
-      <x:c r="A26" s="4"/>
-      <x:c r="B26" s="4"/>
-      <x:c r="C26" s="4"/>
-      <x:c r="D26" s="4"/>
-      <x:c r="E26" s="4"/>
-      <x:c r="F26" s="4"/>
-      <x:c r="G26" s="4"/>
-      <x:c r="H26" s="4"/>
-      <x:c r="I26" s="4"/>
-      <x:c r="J26" s="4"/>
-      <x:c r="K26" s="4"/>
-    </x:row>
-    <x:row r="27" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A27" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B27" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C27" s="11" t="s">
+      <x:c r="J26" s="11" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D27" s="11" t="s">
+      <x:c r="K26" s="11" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E27" s="11" t="s">
+    </x:row>
+    <x:row r="27" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A27" s="12" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F27" s="11" t="s">
+      <x:c r="B27" s="12" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G27" s="11" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H27" s="11" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="I27" s="11" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="J27" s="11" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="K27" s="11" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A28" s="12" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B28" s="12" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C28" s="12" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D28" s="12" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E28" s="12" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F28" s="12" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G28" s="12" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H28" s="12" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="I28" s="12" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="J28" s="12" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="K28" s="12" t="s">
-        <x:v>78</x:v>
+      <x:c r="C27" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D27" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E27" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F27" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G27" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H27" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="I27" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="J27" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="K27" s="12" t="s">
+        <x:v>71</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1400,8 +1350,8 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A18:F18"/>
-    <x:mergeCell ref="A25:J25"/>
+    <x:mergeCell ref="A17:F17"/>
+    <x:mergeCell ref="A24:J24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 29/06/2026, 11:43</x:t>
+    <x:t>Conta: 7983962 | 30/06/2026, 20:06</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>10,3%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.013.621,38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,20%|Pós-Fixada</x:t>
+    <x:t>17,3%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.014.071,31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,20%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>48,8%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.815.317,82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48,80%|Pós-Fixada</x:t>
+    <x:t>13,9%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 813.439,04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13,80%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>16/06/2026</x:t>
@@ -112,22 +112,22 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>3.218.748,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.795.935,42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.810.956,78</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40,9%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.036.528,33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40,90%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>543.492,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 809.803,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 812.620,98</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68,8%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.038.656,34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -145,10 +145,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>29/06/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.410,38</x:t>
+    <x:t>30/06/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.411,11</x:t>
   </x:si>
   <x:si>
     <x:t>1.070,72</x:t>
@@ -157,10 +157,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.510.119,79</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.507.063,82</x:t>
+    <x:t>R$ 1.510.899,08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.507.383,33</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -172,31 +172,31 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 508.566,26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 506.834,56</x:t>
+    <x:t>R$ 508.897,78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 507.091,48</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 138,56</x:t>
+    <x:t>R$ 138,63</x:t>
   </x:si>
   <x:si>
     <x:t>14.562,54</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.017.842,28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.013.264,81</x:t>
+    <x:t>R$ 2.018.859,48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.013.775,20</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 686,01</x:t>
+    <x:t>R$ 685,69</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -226,7 +226,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>686,01</x:t>
+    <x:t>685,69</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -834,13 +834,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>9866153.538826</x:v>
+        <x:v>5866852.38315</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>9865467.528826</x:v>
+        <x:v>5866166.69315</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>686.01</x:v>
+        <x:v>685.69</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 30/06/2026, 20:06</x:t>
+    <x:t>Conta: 7983962 | 01/07/2026, 18:17</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>17,3%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.014.071,31</x:t>
+    <x:t>R$ 1.014.521,44</x:t>
   </x:si>
   <x:si>
     <x:t>17,20%|Pós-Fixada</x:t>
@@ -97,7 +97,7 @@
     <x:t>13,9%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 813.439,04</x:t>
+    <x:t>R$ 813.802,09</x:t>
   </x:si>
   <x:si>
     <x:t>13,80%|Pós-Fixada</x:t>
@@ -118,13 +118,13 @@
     <x:t>R$ 809.803,23</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 812.620,98</x:t>
+    <x:t>R$ 812.902,35</x:t>
   </x:si>
   <x:si>
     <x:t>68,8%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.038.656,34</x:t>
+    <x:t>R$ 4.040.775,08</x:t>
   </x:si>
   <x:si>
     <x:t>68,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -145,10 +145,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>30/06/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.411,11</x:t>
+    <x:t>01/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.411,89</x:t>
   </x:si>
   <x:si>
     <x:t>1.070,72</x:t>
@@ -157,10 +157,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.510.899,08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.507.383,33</x:t>
+    <x:t>R$ 1.511.732,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.507.767,74</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -172,25 +172,25 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 508.897,78</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 507.091,48</x:t>
+    <x:t>R$ 509.167,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 507.300,32</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 138,63</x:t>
+    <x:t>R$ 138,70</x:t>
   </x:si>
   <x:si>
     <x:t>14.562,54</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.018.859,48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.013.775,20</x:t>
+    <x:t>R$ 2.019.875,20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.014.327,86</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
@@ -834,10 +834,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5866852.38315</x:v>
+        <x:v>5869784.308826</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5866166.69315</x:v>
+        <x:v>5869098.618826</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>685.69</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 01/07/2026, 18:17</x:t>
+    <x:t>Conta: 7983962 | 03/07/2026, 15:18</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>17,3%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.014.521,44</x:t>
+    <x:t>R$ 1.015.422,31</x:t>
   </x:si>
   <x:si>
     <x:t>17,20%|Pós-Fixada</x:t>
@@ -97,7 +97,7 @@
     <x:t>13,9%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 813.802,09</x:t>
+    <x:t>R$ 814.529,29</x:t>
   </x:si>
   <x:si>
     <x:t>13,80%|Pós-Fixada</x:t>
@@ -118,7 +118,7 @@
     <x:t>R$ 809.803,23</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 812.902,35</x:t>
+    <x:t>R$ 813.465,93</x:t>
   </x:si>
   <x:si>
     <x:t>68,8%|Fundos de Investimento</x:t>
@@ -834,10 +834,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5869784.308826</x:v>
+        <x:v>5871412.366682</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5869098.618826</x:v>
+        <x:v>5870726.676682</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>685.69</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 03/07/2026, 15:18</x:t>
+    <x:t>Conta: 7983962 | 06/07/2026, 17:12</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>17,3%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.015.422,31</x:t>
+    <x:t>R$ 1.015.873,04</x:t>
   </x:si>
   <x:si>
     <x:t>17,20%|Pós-Fixada</x:t>
@@ -97,7 +97,7 @@
     <x:t>13,9%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 814.529,29</x:t>
+    <x:t>R$ 814.892,88</x:t>
   </x:si>
   <x:si>
     <x:t>13,80%|Pós-Fixada</x:t>
@@ -118,13 +118,13 @@
     <x:t>R$ 809.803,23</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 813.465,93</x:t>
+    <x:t>R$ 813.747,71</x:t>
   </x:si>
   <x:si>
     <x:t>68,8%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.040.775,08</x:t>
+    <x:t>R$ 4.047.037,89</x:t>
   </x:si>
   <x:si>
     <x:t>68,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -145,10 +145,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>01/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.411,89</x:t>
+    <x:t>06/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.414,06</x:t>
   </x:si>
   <x:si>
     <x:t>1.070,72</x:t>
@@ -157,10 +157,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.511.732,63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.507.767,74</x:t>
+    <x:t>R$ 1.514.059,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.509.178,28</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -172,25 +172,25 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 509.167,25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 507.300,32</x:t>
+    <x:t>R$ 510.074,49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 508.003,43</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 138,70</x:t>
+    <x:t>R$ 138,91</x:t>
   </x:si>
   <x:si>
     <x:t>14.562,54</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.019.875,20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.014.327,86</x:t>
+    <x:t>R$ 2.022.903,57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.016.288,04</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
@@ -834,10 +834,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5871412.366682</x:v>
+        <x:v>5878489.50554</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5870726.676682</x:v>
+        <x:v>5877803.81554</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>685.69</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 06/07/2026, 17:12</x:t>
+    <x:t>Conta: 7983962 | 07/07/2026, 15:56</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>17,3%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.015.873,04</x:t>
+    <x:t>R$ 1.016.323,98</x:t>
   </x:si>
   <x:si>
     <x:t>17,20%|Pós-Fixada</x:t>
@@ -97,7 +97,7 @@
     <x:t>13,9%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 814.892,88</x:t>
+    <x:t>R$ 815.256,48</x:t>
   </x:si>
   <x:si>
     <x:t>13,80%|Pós-Fixada</x:t>
@@ -118,13 +118,13 @@
     <x:t>R$ 809.803,23</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 813.747,71</x:t>
+    <x:t>R$ 814.029,50</x:t>
   </x:si>
   <x:si>
     <x:t>68,8%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.047.037,89</x:t>
+    <x:t>R$ 4.049.172,95</x:t>
   </x:si>
   <x:si>
     <x:t>68,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -145,10 +145,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>06/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.414,06</x:t>
+    <x:t>07/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.414,85</x:t>
   </x:si>
   <x:si>
     <x:t>1.070,72</x:t>
@@ -157,10 +157,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.514.059,83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.509.178,28</x:t>
+    <x:t>R$ 1.514.910,48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.509.721,71</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -172,25 +172,25 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 510.074,49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 508.003,43</x:t>
+    <x:t>R$ 510.348,48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 508.215,78</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 138,91</x:t>
+    <x:t>R$ 138,98</x:t>
   </x:si>
   <x:si>
     <x:t>14.562,54</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.022.903,57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.016.288,04</x:t>
+    <x:t>R$ 2.023.913,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.016.978,10</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
@@ -834,10 +834,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5878489.50554</x:v>
+        <x:v>5881439.094478</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5877803.81554</x:v>
+        <x:v>5880753.404478</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>685.69</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 07/07/2026, 15:56</x:t>
+    <x:t>Conta: 7983962 | 09/07/2026, 18:03</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>17,3%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.016.323,98</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17,20%|Pós-Fixada</x:t>
+    <x:t>17,9%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.017.226,44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,80%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>13,9%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 815.256,48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13,80%|Pós-Fixada</x:t>
+    <x:t>10,8%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 615.572,35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,80%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>16/06/2026</x:t>
@@ -112,22 +112,22 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>543.492,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 809.803,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 814.029,50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>68,8%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.049.172,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>68,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>410.006,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 610.909,05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 614.523,11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71,3%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.053.291,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71,20%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -145,10 +145,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>07/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.414,85</x:t>
+    <x:t>09/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.416,33</x:t>
   </x:si>
   <x:si>
     <x:t>1.070,72</x:t>
@@ -157,46 +157,46 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.514.910,48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.509.721,71</x:t>
+    <x:t>R$ 1.516.491,33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.510.760,34</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,44</x:t>
+    <x:t>R$ 1,45</x:t>
   </x:si>
   <x:si>
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 510.348,48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 508.215,78</x:t>
+    <x:t>R$ 510.888,73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 508.634,47</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 138,98</x:t>
+    <x:t>R$ 139,12</x:t>
   </x:si>
   <x:si>
     <x:t>14.562,54</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.023.913,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.016.978,10</x:t>
+    <x:t>R$ 2.025.911,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.018.352,17</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 685,69</x:t>
+    <x:t>R$ 687,09</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -226,7 +226,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>685,69</x:t>
+    <x:t>687,09</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -834,13 +834,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5881439.094478</x:v>
+        <x:v>5686777.310144</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5880753.404478</x:v>
+        <x:v>5686090.220144</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>685.69</x:v>
+        <x:v>687.09</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 09/07/2026, 18:03</x:t>
+    <x:t>Conta: 7983962 | 14/07/2026, 09:57</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>17,9%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.017.226,44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17,80%|Pós-Fixada</x:t>
+    <x:t>20,4%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.018.581,64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,30%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>10,8%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 615.572,35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,80%|Pós-Fixada</x:t>
+    <x:t>0,23%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 11.264,87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,22%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>16/06/2026</x:t>
@@ -112,22 +112,22 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>410.006,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 610.909,05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 614.523,11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>71,3%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.053.291,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>71,20%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>7.493,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 11.164,57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 11.242,30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79,3%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.958.362,80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79,20%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -145,10 +145,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>09/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.416,33</x:t>
+    <x:t>14/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.418,74</x:t>
   </x:si>
   <x:si>
     <x:t>1.070,72</x:t>
@@ -157,10 +157,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.516.491,33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.510.760,34</x:t>
+    <x:t>R$ 1.519.073,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.513.084,27</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -172,31 +172,34 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 510.888,73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 508.634,47</x:t>
+    <x:t>R$ 511.822,30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 509.357,99</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 139,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.562,54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.025.911,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.018.352,17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,01%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 687,09</x:t>
+    <x:t>13/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 139,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.840,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.927.467,07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.920.193,29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,12%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 6.079,31</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -226,7 +229,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>687,09</x:t>
+    <x:t>6079,31</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -834,13 +837,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5686777.310144</x:v>
+        <x:v>4994288.625198</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5686090.220144</x:v>
+        <x:v>4988209.315198</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>687.09</x:v>
+        <x:v>6079.31</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1209,22 +1212,22 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C22" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="F22" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
@@ -1246,7 +1249,7 @@
     </x:row>
     <x:row r="24" spans="1:11" ht="45" customHeight="1">
       <x:c r="A24" s="8" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B24" s="9"/>
       <x:c r="C24" s="9"/>
@@ -1258,7 +1261,7 @@
       <x:c r="I24" s="9"/>
       <x:c r="J24" s="9"/>
       <x:c r="K24" s="10" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -1282,66 +1285,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D26" s="11" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E26" s="11" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F26" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G26" s="11" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H26" s="11" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I26" s="11" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="J26" s="11" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="K26" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11" ht="30" customHeight="1">
       <x:c r="A27" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B27" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C27" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D27" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E27" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F27" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G27" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H27" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I27" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J27" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K27" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 14/07/2026, 09:57</x:t>
+    <x:t>Conta: 7983962 | 15/07/2026, 19:00</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>20,4%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.018.581,64</x:t>
+    <x:t>R$ 1.019.033,78</x:t>
   </x:si>
   <x:si>
     <x:t>20,30%|Pós-Fixada</x:t>
@@ -97,7 +97,7 @@
     <x:t>0,23%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 11.264,87</x:t>
+    <x:t>R$ 11.269,90</x:t>
   </x:si>
   <x:si>
     <x:t>0,22%|Pós-Fixada</x:t>
@@ -118,13 +118,13 @@
     <x:t>R$ 11.164,57</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 11.242,30</x:t>
+    <x:t>R$ 11.246,20</x:t>
   </x:si>
   <x:si>
     <x:t>79,3%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 3.958.362,80</x:t>
+    <x:t>R$ 3.961.274,12</x:t>
   </x:si>
   <x:si>
     <x:t>79,20%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -145,10 +145,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>14/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.418,74</x:t>
+    <x:t>15/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.419,42</x:t>
   </x:si>
   <x:si>
     <x:t>1.070,72</x:t>
@@ -157,10 +157,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.519.073,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.513.084,27</x:t>
+    <x:t>R$ 1.519.799,14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.513.708,87</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -172,28 +172,25 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 511.822,30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 509.357,99</x:t>
+    <x:t>R$ 512.093,71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 509.568,33</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>13/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 139,26</x:t>
+    <x:t>R$ 139,40</x:t>
   </x:si>
   <x:si>
     <x:t>13.840,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.927.467,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.920.193,29</x:t>
+    <x:t>R$ 1.929.381,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.921.748,19</x:t>
   </x:si>
   <x:si>
     <x:t>0,12%|Saldo projetado</x:t>
@@ -837,10 +834,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4994288.625198</x:v>
+        <x:v>4997657.108101</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4988209.315198</x:v>
+        <x:v>4991577.798101</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>6079.31</x:v>
@@ -1212,22 +1209,22 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C22" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C22" s="12" t="s">
+      <x:c r="D22" s="12" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="D22" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="F22" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G22" s="12" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="G22" s="12" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
@@ -1249,7 +1246,7 @@
     </x:row>
     <x:row r="24" spans="1:11" ht="45" customHeight="1">
       <x:c r="A24" s="8" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B24" s="9"/>
       <x:c r="C24" s="9"/>
@@ -1261,7 +1258,7 @@
       <x:c r="I24" s="9"/>
       <x:c r="J24" s="9"/>
       <x:c r="K24" s="10" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -1285,66 +1282,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D26" s="11" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D26" s="11" t="s">
+      <x:c r="E26" s="11" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="E26" s="11" t="s">
+      <x:c r="F26" s="11" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="F26" s="11" t="s">
+      <x:c r="G26" s="11" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G26" s="11" t="s">
+      <x:c r="H26" s="11" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="H26" s="11" t="s">
+      <x:c r="I26" s="11" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="I26" s="11" t="s">
+      <x:c r="J26" s="11" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="J26" s="11" t="s">
+      <x:c r="K26" s="11" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="K26" s="11" t="s">
-        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11" ht="30" customHeight="1">
       <x:c r="A27" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B27" s="12" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B27" s="12" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="C27" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D27" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E27" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F27" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G27" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H27" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I27" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J27" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K27" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 15/07/2026, 19:00</x:t>
+    <x:t>Conta: 7983962 | 21/07/2026, 09:17</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>20,4%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.019.033,78</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20,30%|Pós-Fixada</x:t>
+    <x:t>23,7%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.020.844,33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23,70%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,40 +94,13 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>0,23%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 11.269,90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,22%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/06/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.493,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 11.164,57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 11.246,20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79,3%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.961.274,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79,20%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>76,2%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.277.475,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>76,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -145,10 +118,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>15/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.419,42</x:t>
+    <x:t>20/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.421,70</x:t>
   </x:si>
   <x:si>
     <x:t>1.070,72</x:t>
@@ -157,10 +130,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.519.799,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.513.708,87</x:t>
+    <x:t>R$ 1.522.244,42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.516.490,37</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -172,31 +145,31 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 512.093,71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 509.568,33</x:t>
+    <x:t>R$ 512.907,42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 510.198,95</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 139,40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.840,86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.929.381,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.921.748,19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,12%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 6.079,31</x:t>
+    <x:t>R$ 139,61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.898,52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.242.323,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.238.231,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,09%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.964,00</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -226,7 +199,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>6079,31</x:t>
+    <x:t>3964</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -774,7 +747,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K27"/>
+  <x:dimension ref="A1:K22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -834,13 +807,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4997657.108101</x:v>
+        <x:v>4302283.79726</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4991577.798101</x:v>
+        <x:v>4298319.79726</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>6079.31</x:v>
+        <x:v>3964</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1023,87 +996,103 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D14" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E14" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F14" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G14" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I14" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
+      <x:c r="H14" s="3"/>
+      <x:c r="I14" s="3"/>
+      <x:c r="J14" s="3"/>
       <x:c r="K14" s="3"/>
     </x:row>
     <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="12"/>
-      <x:c r="B15" s="12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C15" s="12"/>
-      <x:c r="D15" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E15" s="12" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F15" s="12" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G15" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H15" s="12" t="s">
+      <x:c r="A15" s="13" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="I15" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="s">
+      <x:c r="B15" s="13" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="C15" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H15" s="3"/>
+      <x:c r="I15" s="3"/>
+      <x:c r="J15" s="3"/>
       <x:c r="K15" s="3"/>
     </x:row>
-    <x:row r="16" spans="1:11">
-      <x:c r="A16" s="4"/>
-      <x:c r="B16" s="4"/>
-      <x:c r="C16" s="4"/>
-      <x:c r="D16" s="4"/>
-      <x:c r="E16" s="4"/>
-      <x:c r="F16" s="4"/>
-      <x:c r="G16" s="4"/>
-      <x:c r="H16" s="4"/>
-      <x:c r="I16" s="4"/>
-      <x:c r="J16" s="4"/>
-      <x:c r="K16" s="4"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A17" s="8" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B17" s="9"/>
-      <x:c r="C17" s="9"/>
-      <x:c r="D17" s="9"/>
-      <x:c r="E17" s="9"/>
-      <x:c r="F17" s="9"/>
-      <x:c r="G17" s="10" t="s">
-        <x:v>36</x:v>
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H16" s="3"/>
+      <x:c r="I16" s="3"/>
+      <x:c r="J16" s="3"/>
+      <x:c r="K16" s="3"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A17" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B17" s="12" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C17" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E17" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F17" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G17" s="12" t="s">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
@@ -1118,240 +1107,118 @@
       <x:c r="E18" s="4"/>
       <x:c r="F18" s="4"/>
       <x:c r="G18" s="4"/>
-      <x:c r="H18" s="3"/>
-      <x:c r="I18" s="3"/>
-      <x:c r="J18" s="3"/>
-      <x:c r="K18" s="3"/>
-    </x:row>
-    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A19" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B19" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D19" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H19" s="3"/>
-      <x:c r="I19" s="3"/>
-      <x:c r="J19" s="3"/>
-      <x:c r="K19" s="3"/>
-    </x:row>
-    <x:row r="20" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A20" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B20" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C20" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D20" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E20" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F20" s="13" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G20" s="13" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H20" s="3"/>
-      <x:c r="I20" s="3"/>
-      <x:c r="J20" s="3"/>
-      <x:c r="K20" s="3"/>
-    </x:row>
-    <x:row r="21" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A21" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B21" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C21" s="13" t="s">
+      <x:c r="H18" s="4"/>
+      <x:c r="I18" s="4"/>
+      <x:c r="J18" s="4"/>
+      <x:c r="K18" s="4"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A19" s="8" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D21" s="13" t="s">
+      <x:c r="B19" s="9"/>
+      <x:c r="C19" s="9"/>
+      <x:c r="D19" s="9"/>
+      <x:c r="E19" s="9"/>
+      <x:c r="F19" s="9"/>
+      <x:c r="G19" s="9"/>
+      <x:c r="H19" s="9"/>
+      <x:c r="I19" s="9"/>
+      <x:c r="J19" s="9"/>
+      <x:c r="K19" s="10" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="E21" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F21" s="13" t="s">
+    </x:row>
+    <x:row r="20" spans="1:11">
+      <x:c r="A20" s="4"/>
+      <x:c r="B20" s="4"/>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="4"/>
+      <x:c r="E20" s="4"/>
+      <x:c r="F20" s="4"/>
+      <x:c r="G20" s="4"/>
+      <x:c r="H20" s="4"/>
+      <x:c r="I20" s="4"/>
+      <x:c r="J20" s="4"/>
+      <x:c r="K20" s="4"/>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A21" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G21" s="13" t="s">
+      <x:c r="D21" s="11" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H21" s="3"/>
-      <x:c r="I21" s="3"/>
-      <x:c r="J21" s="3"/>
-      <x:c r="K21" s="3"/>
+      <x:c r="E21" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H21" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I21" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J21" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K21" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
       <x:c r="A22" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C22" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F22" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G22" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H22" s="3"/>
-      <x:c r="I22" s="3"/>
-      <x:c r="J22" s="3"/>
-      <x:c r="K22" s="3"/>
-    </x:row>
-    <x:row r="23" spans="1:11">
-      <x:c r="A23" s="4"/>
-      <x:c r="B23" s="4"/>
-      <x:c r="C23" s="4"/>
-      <x:c r="D23" s="4"/>
-      <x:c r="E23" s="4"/>
-      <x:c r="F23" s="4"/>
-      <x:c r="G23" s="4"/>
-      <x:c r="H23" s="4"/>
-      <x:c r="I23" s="4"/>
-      <x:c r="J23" s="4"/>
-      <x:c r="K23" s="4"/>
-    </x:row>
-    <x:row r="24" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A24" s="8" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B24" s="9"/>
-      <x:c r="C24" s="9"/>
-      <x:c r="D24" s="9"/>
-      <x:c r="E24" s="9"/>
-      <x:c r="F24" s="9"/>
-      <x:c r="G24" s="9"/>
-      <x:c r="H24" s="9"/>
-      <x:c r="I24" s="9"/>
-      <x:c r="J24" s="9"/>
-      <x:c r="K24" s="10" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:11">
-      <x:c r="A25" s="4"/>
-      <x:c r="B25" s="4"/>
-      <x:c r="C25" s="4"/>
-      <x:c r="D25" s="4"/>
-      <x:c r="E25" s="4"/>
-      <x:c r="F25" s="4"/>
-      <x:c r="G25" s="4"/>
-      <x:c r="H25" s="4"/>
-      <x:c r="I25" s="4"/>
-      <x:c r="J25" s="4"/>
-      <x:c r="K25" s="4"/>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A26" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B26" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C26" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D26" s="11" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="E26" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F26" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G26" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H26" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="I26" s="11" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="J26" s="11" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="K26" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A27" s="12" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B27" s="12" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C27" s="12" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D27" s="12" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E27" s="12" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F27" s="12" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G27" s="12" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H27" s="12" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="I27" s="12" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="J27" s="12" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="K27" s="12" t="s">
-        <x:v>71</x:v>
+      <x:c r="H22" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I22" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J22" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K22" s="12" t="s">
+        <x:v>62</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="6">
+  <x:mergeCells count="5">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A17:F17"/>
-    <x:mergeCell ref="A24:J24"/>
+    <x:mergeCell ref="A19:J19"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 21/07/2026, 09:17</x:t>
+    <x:t>Conta: 7983962 | 27/07/2026, 15:22</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>23,7%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.020.844,33</x:t>
+    <x:t>R$ 1.022.658,09</x:t>
   </x:si>
   <x:si>
     <x:t>23,70%|Pós-Fixada</x:t>
@@ -97,7 +97,7 @@
     <x:t>76,2%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 3.277.475,47</x:t>
+    <x:t>R$ 3.285.506,07</x:t>
   </x:si>
   <x:si>
     <x:t>76,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -118,10 +118,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>20/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.421,70</x:t>
+    <x:t>27/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.425,44</x:t>
   </x:si>
   <x:si>
     <x:t>1.070,72</x:t>
@@ -130,40 +130,43 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.522.244,42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.516.490,37</x:t>
+    <x:t>R$ 1.526.240,49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.520.553,52</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,45</x:t>
+    <x:t>R$ 1,46</x:t>
   </x:si>
   <x:si>
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 512.907,42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 510.198,95</x:t>
+    <x:t>R$ 514.314,28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 511.289,27</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 139,61</x:t>
+    <x:t>24/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 139,91</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.242.323,63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.238.231,58</x:t>
+    <x:t>R$ 1.244.951,30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.241.181,78</x:t>
   </x:si>
   <x:si>
     <x:t>0,09%|Saldo projetado</x:t>
@@ -807,10 +810,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4302283.79726</x:v>
+        <x:v>4312128.16237</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4298319.79726</x:v>
+        <x:v>4308164.16237</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>3964</x:v>
@@ -1077,22 +1080,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="12" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C17" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D17" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="F17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
@@ -1114,7 +1117,7 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="45" customHeight="1">
       <x:c r="A19" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="9"/>
@@ -1126,7 +1129,7 @@
       <x:c r="I19" s="9"/>
       <x:c r="J19" s="9"/>
       <x:c r="K19" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
@@ -1150,66 +1153,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="11" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D21" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E21" s="11" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F21" s="11" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G21" s="11" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H21" s="11" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I21" s="11" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J21" s="11" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K21" s="11" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
       <x:c r="A22" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C22" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F22" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G22" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H22" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I22" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J22" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K22" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 27/07/2026, 15:22</x:t>
+    <x:t>Conta: 7983962 | 29/07/2026, 18:27</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>23,7%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.022.658,09</x:t>
+    <x:t>R$ 1.023.566,18</x:t>
   </x:si>
   <x:si>
     <x:t>23,70%|Pós-Fixada</x:t>
@@ -97,7 +97,7 @@
     <x:t>76,2%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 3.285.506,07</x:t>
+    <x:t>R$ 3.289.414,14</x:t>
   </x:si>
   <x:si>
     <x:t>76,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -118,10 +118,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>27/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.425,44</x:t>
+    <x:t>29/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.426,83</x:t>
   </x:si>
   <x:si>
     <x:t>1.070,72</x:t>
@@ -130,10 +130,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.526.240,49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.520.553,52</x:t>
+    <x:t>R$ 1.527.736,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.521.712,88</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -145,28 +145,25 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 514.314,28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 511.289,27</x:t>
+    <x:t>R$ 514.859,12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 511.711,52</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>24/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 139,91</x:t>
+    <x:t>R$ 140,12</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.244.951,30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.241.181,78</x:t>
+    <x:t>R$ 1.246.818,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.242.628,92</x:t>
   </x:si>
   <x:si>
     <x:t>0,09%|Saldo projetado</x:t>
@@ -810,10 +807,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4312128.16237</x:v>
+        <x:v>4316944.32303</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4308164.16237</x:v>
+        <x:v>4312980.32303</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>3964</x:v>
@@ -1080,22 +1077,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="12" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C17" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C17" s="12" t="s">
+      <x:c r="D17" s="12" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="D17" s="12" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="F17" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G17" s="12" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="G17" s="12" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
@@ -1117,7 +1114,7 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="45" customHeight="1">
       <x:c r="A19" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="9"/>
@@ -1129,7 +1126,7 @@
       <x:c r="I19" s="9"/>
       <x:c r="J19" s="9"/>
       <x:c r="K19" s="10" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
@@ -1153,66 +1150,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D21" s="11" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D21" s="11" t="s">
+      <x:c r="E21" s="11" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E21" s="11" t="s">
+      <x:c r="F21" s="11" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="s">
+      <x:c r="G21" s="11" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G21" s="11" t="s">
+      <x:c r="H21" s="11" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H21" s="11" t="s">
+      <x:c r="I21" s="11" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="I21" s="11" t="s">
+      <x:c r="J21" s="11" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="J21" s="11" t="s">
+      <x:c r="K21" s="11" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="K21" s="11" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
       <x:c r="A22" s="12" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B22" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="C22" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F22" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G22" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H22" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I22" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J22" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K22" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 29/07/2026, 18:27</x:t>
+    <x:t>Conta: 7983962 | 30/07/2026, 16:36</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>23,7%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.023.566,18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23,70%|Pós-Fixada</x:t>
+    <x:t>36,4%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.024.020,53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,40%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>76,2%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.289.414,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>76,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>63,4%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.784.314,46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63,40%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -118,22 +118,22 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>29/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.426,83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.070,72</x:t>
+    <x:t>30/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.427,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,17</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.527.736,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.521.712,88</x:t>
+    <x:t>R$ 21.657,75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 21.591,21</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -145,31 +145,31 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 514.859,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 511.711,52</x:t>
+    <x:t>R$ 515.222,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 511.993,42</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 140,12</x:t>
+    <x:t>R$ 140,18</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.246.818,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.242.628,92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,09%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.964,00</x:t>
+    <x:t>R$ 1.247.433,85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.243.105,75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,17%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.799,69</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -199,7 +199,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>3964</x:t>
+    <x:t>4799,69</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -807,13 +807,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4316944.32303</x:v>
+        <x:v>2813134.6807</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4312980.32303</x:v>
+        <x:v>2808334.9907</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>3964</x:v>
+        <x:v>4799.69</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 30/07/2026, 16:36</x:t>
+    <x:t>Conta: 7983962 | 04/08/2026, 17:39</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,10 +37,10 @@
     <x:t>36,4%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.024.020,53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36,40%|Pós-Fixada</x:t>
+    <x:t>R$ 1.025.384,78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,30%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -97,7 +97,7 @@
     <x:t>63,4%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.784.314,46</x:t>
+    <x:t>R$ 1.786.959,49</x:t>
   </x:si>
   <x:si>
     <x:t>63,40%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -118,10 +118,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>30/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.427,69</x:t>
+    <x:t>04/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.429,94</x:t>
   </x:si>
   <x:si>
     <x:t>15,17</x:t>
@@ -130,10 +130,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 21.657,75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 21.591,21</x:t>
+    <x:t>R$ 21.691,80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 21.617,60</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -145,25 +145,25 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 515.222,86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 511.993,42</x:t>
+    <x:t>R$ 516.047,14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 512.632,24</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 140,18</x:t>
+    <x:t>R$ 140,39</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.247.433,85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.243.105,75</x:t>
+    <x:t>R$ 1.249.220,55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.244.490,44</x:t>
   </x:si>
   <x:si>
     <x:t>0,17%|Saldo projetado</x:t>
@@ -807,10 +807,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2813134.6807</x:v>
+        <x:v>2817143.96415</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>2808334.9907</x:v>
+        <x:v>2812344.27415</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>4799.69</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 04/08/2026, 17:39</x:t>
+    <x:t>Conta: 7983962 | 11/08/2026, 16:36</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,10 +37,10 @@
     <x:t>36,4%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.025.384,78</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36,30%|Pós-Fixada</x:t>
+    <x:t>R$ 1.027.639,90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,40%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -97,7 +97,7 @@
     <x:t>63,4%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.786.959,49</x:t>
+    <x:t>R$ 1.790.605,17</x:t>
   </x:si>
   <x:si>
     <x:t>63,40%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -118,10 +118,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>04/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.429,94</x:t>
+    <x:t>10/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.432,82</x:t>
   </x:si>
   <x:si>
     <x:t>15,17</x:t>
@@ -130,10 +130,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 21.691,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 21.617,60</x:t>
+    <x:t>R$ 21.735,48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 21.651,46</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -145,25 +145,25 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 516.047,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 512.632,24</x:t>
+    <x:t>R$ 517.123,53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 513.466,44</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 140,39</x:t>
+    <x:t>R$ 140,67</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.249.220,55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.244.490,44</x:t>
+    <x:t>R$ 1.251.746,16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.246.447,79</x:t>
   </x:si>
   <x:si>
     <x:t>0,17%|Saldo projetado</x:t>
@@ -807,10 +807,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2817143.96415</x:v>
+        <x:v>2823044.75964</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>2812344.27415</x:v>
+        <x:v>2818245.06964</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>4799.69</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 11/08/2026, 16:36</x:t>
+    <x:t>Conta: 7983962 | 17/08/2026, 14:24</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>36,4%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.027.639,90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36,40%|Pós-Fixada</x:t>
+    <x:t>23,2%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.029.435,45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23,20%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,34 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>63,4%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.790.605,17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>63,40%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>36,2%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.603.779,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,20%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.015.050,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,5%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.795.215,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -118,10 +139,7 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>10/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.432,82</x:t>
+    <x:t>R$ 1.436,71</x:t>
   </x:si>
   <x:si>
     <x:t>15,17</x:t>
@@ -130,46 +148,43 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 21.735,48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 21.651,46</x:t>
+    <x:t>R$ 21.794,52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 21.697,21</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,46</x:t>
+    <x:t>R$ 1,47</x:t>
   </x:si>
   <x:si>
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 517.123,53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 513.466,44</x:t>
+    <x:t>R$ 518.551,73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 514.573,29</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 140,67</x:t>
+    <x:t>R$ 141,02</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.251.746,16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.246.447,79</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,17%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.799,69</x:t>
+    <x:t>R$ 1.254.869,34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.248.868,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,83</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -199,7 +214,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>4799,69</x:t>
+    <x:t>0,83</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -747,7 +762,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K22"/>
+  <x:dimension ref="A1:K27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -807,13 +822,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2823044.75964</x:v>
+        <x:v>4428431.859919</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>2818245.06964</x:v>
+        <x:v>4428431.029919</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>4799.69</x:v>
+        <x:v>0.83</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -996,103 +1011,87 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="3"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="12"/>
+      <x:c r="B15" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="s">
+      <x:c r="C15" s="12"/>
+      <x:c r="D15" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="s">
+      <x:c r="E15" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="F15" s="12" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H14" s="3"/>
-      <x:c r="I14" s="3"/>
-      <x:c r="J14" s="3"/>
-      <x:c r="K14" s="3"/>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="13" t="s">
+      <x:c r="G15" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="1:11">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="4"/>
+      <x:c r="C16" s="4"/>
+      <x:c r="D16" s="4"/>
+      <x:c r="E16" s="4"/>
+      <x:c r="F16" s="4"/>
+      <x:c r="G16" s="4"/>
+      <x:c r="H16" s="4"/>
+      <x:c r="I16" s="4"/>
+      <x:c r="J16" s="4"/>
+      <x:c r="K16" s="4"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A17" s="8" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B15" s="13" t="s">
+      <x:c r="B17" s="9"/>
+      <x:c r="C17" s="9"/>
+      <x:c r="D17" s="9"/>
+      <x:c r="E17" s="9"/>
+      <x:c r="F17" s="9"/>
+      <x:c r="G17" s="10" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="C15" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D15" s="13" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E15" s="13" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F15" s="13" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G15" s="13" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H15" s="3"/>
-      <x:c r="I15" s="3"/>
-      <x:c r="J15" s="3"/>
-      <x:c r="K15" s="3"/>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="13" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B16" s="13" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C16" s="13" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D16" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E16" s="13" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H16" s="3"/>
-      <x:c r="I16" s="3"/>
-      <x:c r="J16" s="3"/>
-      <x:c r="K16" s="3"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A17" s="12" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B17" s="12" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C17" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D17" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E17" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F17" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G17" s="12" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
@@ -1107,118 +1106,240 @@
       <x:c r="E18" s="4"/>
       <x:c r="F18" s="4"/>
       <x:c r="G18" s="4"/>
-      <x:c r="H18" s="4"/>
-      <x:c r="I18" s="4"/>
-      <x:c r="J18" s="4"/>
-      <x:c r="K18" s="4"/>
-    </x:row>
-    <x:row r="19" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A19" s="8" t="s">
+      <x:c r="H18" s="3"/>
+      <x:c r="I18" s="3"/>
+      <x:c r="J18" s="3"/>
+      <x:c r="K18" s="3"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A19" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H19" s="3"/>
+      <x:c r="I19" s="3"/>
+      <x:c r="J19" s="3"/>
+      <x:c r="K19" s="3"/>
+    </x:row>
+    <x:row r="20" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A20" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D20" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G20" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H20" s="3"/>
+      <x:c r="I20" s="3"/>
+      <x:c r="J20" s="3"/>
+      <x:c r="K20" s="3"/>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A21" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B19" s="9"/>
-      <x:c r="C19" s="9"/>
-      <x:c r="D19" s="9"/>
-      <x:c r="E19" s="9"/>
-      <x:c r="F19" s="9"/>
-      <x:c r="G19" s="9"/>
-      <x:c r="H19" s="9"/>
-      <x:c r="I19" s="9"/>
-      <x:c r="J19" s="9"/>
-      <x:c r="K19" s="10" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:11">
-      <x:c r="A20" s="4"/>
-      <x:c r="B20" s="4"/>
-      <x:c r="C20" s="4"/>
-      <x:c r="D20" s="4"/>
-      <x:c r="E20" s="4"/>
-      <x:c r="F20" s="4"/>
-      <x:c r="G20" s="4"/>
-      <x:c r="H20" s="4"/>
-      <x:c r="I20" s="4"/>
-      <x:c r="J20" s="4"/>
-      <x:c r="K20" s="4"/>
-    </x:row>
-    <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A21" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B21" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C21" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D21" s="11" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F21" s="11" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H21" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="I21" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="J21" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K21" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
+      <x:c r="H21" s="3"/>
+      <x:c r="I21" s="3"/>
+      <x:c r="J21" s="3"/>
+      <x:c r="K21" s="3"/>
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
       <x:c r="A22" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C22" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E22" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F22" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G22" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H22" s="3"/>
+      <x:c r="I22" s="3"/>
+      <x:c r="J22" s="3"/>
+      <x:c r="K22" s="3"/>
+    </x:row>
+    <x:row r="23" spans="1:11">
+      <x:c r="A23" s="4"/>
+      <x:c r="B23" s="4"/>
+      <x:c r="C23" s="4"/>
+      <x:c r="D23" s="4"/>
+      <x:c r="E23" s="4"/>
+      <x:c r="F23" s="4"/>
+      <x:c r="G23" s="4"/>
+      <x:c r="H23" s="4"/>
+      <x:c r="I23" s="4"/>
+      <x:c r="J23" s="4"/>
+      <x:c r="K23" s="4"/>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A24" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B24" s="9"/>
+      <x:c r="C24" s="9"/>
+      <x:c r="D24" s="9"/>
+      <x:c r="E24" s="9"/>
+      <x:c r="F24" s="9"/>
+      <x:c r="G24" s="9"/>
+      <x:c r="H24" s="9"/>
+      <x:c r="I24" s="9"/>
+      <x:c r="J24" s="9"/>
+      <x:c r="K24" s="10" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:11">
+      <x:c r="A25" s="4"/>
+      <x:c r="B25" s="4"/>
+      <x:c r="C25" s="4"/>
+      <x:c r="D25" s="4"/>
+      <x:c r="E25" s="4"/>
+      <x:c r="F25" s="4"/>
+      <x:c r="G25" s="4"/>
+      <x:c r="H25" s="4"/>
+      <x:c r="I25" s="4"/>
+      <x:c r="J25" s="4"/>
+      <x:c r="K25" s="4"/>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A26" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B26" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C26" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D26" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B22" s="12" t="s">
+      <x:c r="H26" s="11" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C22" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D22" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E22" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F22" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G22" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H22" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="I22" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="J22" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="K22" s="12" t="s">
-        <x:v>62</x:v>
+      <x:c r="I26" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J26" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K26" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A27" s="12" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B27" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C27" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D27" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E27" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F27" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G27" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H27" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I27" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="J27" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K27" s="12" t="s">
+        <x:v>67</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="5">
+  <x:mergeCells count="6">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A19:J19"/>
+    <x:mergeCell ref="A17:F17"/>
+    <x:mergeCell ref="A24:J24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 17/08/2026, 14:24</x:t>
+    <x:t>Conta: 7983962 | 18/08/2026, 09:40</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>23,2%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.029.435,45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23,20%|Pós-Fixada</x:t>
+    <x:t>16,0%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.029.884,82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,00%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,34 +94,55 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>36,2%|Operações Compromissadas</x:t>
+    <x:t>56,1%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.605.362,44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56,00%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.015.050,00</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 1.603.779,99</x:t>
   </x:si>
   <x:si>
-    <x:t>36,20%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.015.050,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40,5%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.795.215,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 1.604.484,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.604.325,78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.273.885,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.878,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.680,61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27,9%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.795.821,92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27,90%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -172,16 +193,19 @@
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,02</x:t>
+    <x:t>18/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 141,09</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.254.869,34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.248.868,26</x:t>
+    <x:t>R$ 1.255.475,67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.249.338,16</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,83</x:t>
@@ -762,7 +786,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K27"/>
+  <x:dimension ref="A1:K28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -822,10 +846,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4428431.859919</x:v>
+        <x:v>6431070.01191805</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4428431.029919</x:v>
+        <x:v>6431069.18191805</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>0.83</x:v>
@@ -1040,125 +1064,127 @@
       <x:c r="K14" s="3"/>
     </x:row>
     <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="12"/>
-      <x:c r="B15" s="12" t="s">
+      <x:c r="A15" s="13"/>
+      <x:c r="B15" s="13" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C15" s="12"/>
-      <x:c r="D15" s="12" t="s">
+      <x:c r="C15" s="13"/>
+      <x:c r="D15" s="13" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E15" s="12" t="s">
+      <x:c r="E15" s="13" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F15" s="12" t="s">
+      <x:c r="F15" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G15" s="12" t="s">
+      <x:c r="G15" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H15" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="I15" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="s">
-        <x:v>27</x:v>
+      <x:c r="H15" s="13" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I15" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J15" s="13" t="s">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K15" s="3"/>
     </x:row>
-    <x:row r="16" spans="1:11">
-      <x:c r="A16" s="4"/>
-      <x:c r="B16" s="4"/>
-      <x:c r="C16" s="4"/>
-      <x:c r="D16" s="4"/>
-      <x:c r="E16" s="4"/>
-      <x:c r="F16" s="4"/>
-      <x:c r="G16" s="4"/>
-      <x:c r="H16" s="4"/>
-      <x:c r="I16" s="4"/>
-      <x:c r="J16" s="4"/>
-      <x:c r="K16" s="4"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A17" s="8" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B17" s="9"/>
-      <x:c r="C17" s="9"/>
-      <x:c r="D17" s="9"/>
-      <x:c r="E17" s="9"/>
-      <x:c r="F17" s="9"/>
-      <x:c r="G17" s="10" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H17" s="3"/>
-      <x:c r="I17" s="3"/>
-      <x:c r="J17" s="3"/>
-      <x:c r="K17" s="3"/>
-    </x:row>
-    <x:row r="18" spans="1:11">
-      <x:c r="A18" s="4"/>
-      <x:c r="B18" s="4"/>
-      <x:c r="C18" s="4"/>
-      <x:c r="D18" s="4"/>
-      <x:c r="E18" s="4"/>
-      <x:c r="F18" s="4"/>
-      <x:c r="G18" s="4"/>
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="12"/>
+      <x:c r="B16" s="12" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C16" s="12"/>
+      <x:c r="D16" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F16" s="12" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G16" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H16" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I16" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K16" s="3"/>
+    </x:row>
+    <x:row r="17" spans="1:11">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="4"/>
+      <x:c r="C17" s="4"/>
+      <x:c r="D17" s="4"/>
+      <x:c r="E17" s="4"/>
+      <x:c r="F17" s="4"/>
+      <x:c r="G17" s="4"/>
+      <x:c r="H17" s="4"/>
+      <x:c r="I17" s="4"/>
+      <x:c r="J17" s="4"/>
+      <x:c r="K17" s="4"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A18" s="8" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B18" s="9"/>
+      <x:c r="C18" s="9"/>
+      <x:c r="D18" s="9"/>
+      <x:c r="E18" s="9"/>
+      <x:c r="F18" s="9"/>
+      <x:c r="G18" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
       <x:c r="J18" s="3"/>
       <x:c r="K18" s="3"/>
     </x:row>
-    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A19" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B19" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D19" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
+    <x:row r="19" spans="1:11">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="4"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+      <x:c r="F19" s="4"/>
+      <x:c r="G19" s="4"/>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A20" s="13" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B20" s="13" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C20" s="13" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D20" s="13" t="s">
+    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A20" s="11" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E20" s="13" t="s">
+      <x:c r="B20" s="11" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F20" s="13" t="s">
+      <x:c r="C20" s="11" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G20" s="13" t="s">
+      <x:c r="D20" s="11" t="s">
         <x:v>45</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
@@ -1167,25 +1193,25 @@
     </x:row>
     <x:row r="21" spans="1:11" ht="30" customHeight="1">
       <x:c r="A21" s="13" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C21" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D21" s="13" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E21" s="13" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F21" s="13" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G21" s="13" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
@@ -1193,143 +1219,170 @@
       <x:c r="K21" s="3"/>
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A22" s="12" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B22" s="12" t="s">
+      <x:c r="A22" s="13" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C22" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D22" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E22" s="12" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F22" s="12" t="s">
+      <x:c r="C22" s="13" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G22" s="12" t="s">
+      <x:c r="D22" s="13" t="s">
         <x:v>55</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G22" s="13" t="s">
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
       <x:c r="J22" s="3"/>
       <x:c r="K22" s="3"/>
     </x:row>
-    <x:row r="23" spans="1:11">
-      <x:c r="A23" s="4"/>
-      <x:c r="B23" s="4"/>
-      <x:c r="C23" s="4"/>
-      <x:c r="D23" s="4"/>
-      <x:c r="E23" s="4"/>
-      <x:c r="F23" s="4"/>
-      <x:c r="G23" s="4"/>
-      <x:c r="H23" s="4"/>
-      <x:c r="I23" s="4"/>
-      <x:c r="J23" s="4"/>
-      <x:c r="K23" s="4"/>
-    </x:row>
-    <x:row r="24" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A24" s="8" t="s">
+    <x:row r="23" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A23" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C23" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E23" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F23" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G23" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H23" s="3"/>
+      <x:c r="I23" s="3"/>
+      <x:c r="J23" s="3"/>
+      <x:c r="K23" s="3"/>
+    </x:row>
+    <x:row r="24" spans="1:11">
+      <x:c r="A24" s="4"/>
+      <x:c r="B24" s="4"/>
+      <x:c r="C24" s="4"/>
+      <x:c r="D24" s="4"/>
+      <x:c r="E24" s="4"/>
+      <x:c r="F24" s="4"/>
+      <x:c r="G24" s="4"/>
+      <x:c r="H24" s="4"/>
+      <x:c r="I24" s="4"/>
+      <x:c r="J24" s="4"/>
+      <x:c r="K24" s="4"/>
+    </x:row>
+    <x:row r="25" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A25" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B24" s="9"/>
-      <x:c r="C24" s="9"/>
-      <x:c r="D24" s="9"/>
-      <x:c r="E24" s="9"/>
-      <x:c r="F24" s="9"/>
-      <x:c r="G24" s="9"/>
-      <x:c r="H24" s="9"/>
-      <x:c r="I24" s="9"/>
-      <x:c r="J24" s="9"/>
-      <x:c r="K24" s="10" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:11">
-      <x:c r="A25" s="4"/>
-      <x:c r="B25" s="4"/>
-      <x:c r="C25" s="4"/>
-      <x:c r="D25" s="4"/>
-      <x:c r="E25" s="4"/>
-      <x:c r="F25" s="4"/>
-      <x:c r="G25" s="4"/>
-      <x:c r="H25" s="4"/>
-      <x:c r="I25" s="4"/>
-      <x:c r="J25" s="4"/>
-      <x:c r="K25" s="4"/>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A26" s="11" t="s">
+      <x:c r="B25" s="9"/>
+      <x:c r="C25" s="9"/>
+      <x:c r="D25" s="9"/>
+      <x:c r="E25" s="9"/>
+      <x:c r="F25" s="9"/>
+      <x:c r="G25" s="9"/>
+      <x:c r="H25" s="9"/>
+      <x:c r="I25" s="9"/>
+      <x:c r="J25" s="9"/>
+      <x:c r="K25" s="10" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:11">
+      <x:c r="A26" s="4"/>
+      <x:c r="B26" s="4"/>
+      <x:c r="C26" s="4"/>
+      <x:c r="D26" s="4"/>
+      <x:c r="E26" s="4"/>
+      <x:c r="F26" s="4"/>
+      <x:c r="G26" s="4"/>
+      <x:c r="H26" s="4"/>
+      <x:c r="I26" s="4"/>
+      <x:c r="J26" s="4"/>
+      <x:c r="K26" s="4"/>
+    </x:row>
+    <x:row r="27" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A27" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B26" s="11" t="s">
+      <x:c r="B27" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C26" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D26" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E26" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F26" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G26" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H26" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="I26" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="J26" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="K26" s="11" t="s">
+      <x:c r="C27" s="11" t="s">
         <x:v>65</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A27" s="12" t="s">
+      <x:c r="D27" s="11" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B27" s="12" t="s">
+      <x:c r="E27" s="11" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C27" s="12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D27" s="12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E27" s="12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F27" s="12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G27" s="12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H27" s="12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I27" s="12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="J27" s="12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="K27" s="12" t="s">
-        <x:v>67</x:v>
+      <x:c r="F27" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G27" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H27" s="11" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I27" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="J27" s="11" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K27" s="11" t="s">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A28" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B28" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C28" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E28" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F28" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G28" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H28" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="I28" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J28" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K28" s="12" t="s">
+        <x:v>75</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1338,8 +1391,8 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A17:F17"/>
-    <x:mergeCell ref="A24:J24"/>
+    <x:mergeCell ref="A18:F18"/>
+    <x:mergeCell ref="A25:J25"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 18/08/2026, 09:40</x:t>
+    <x:t>Conta: 7983962 | 18/08/2026, 18:43</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -139,7 +139,7 @@
     <x:t>27,9%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.795.821,92</x:t>
+    <x:t>R$ 1.796.103,11</x:t>
   </x:si>
   <x:si>
     <x:t>27,90%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -160,7 +160,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.436,71</x:t>
+    <x:t>18/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.437,40</x:t>
   </x:si>
   <x:si>
     <x:t>15,17</x:t>
@@ -169,10 +172,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 21.794,52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 21.697,21</x:t>
+    <x:t>R$ 21.805,04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 21.705,37</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -184,16 +187,13 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 518.551,73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 514.573,29</x:t>
+    <x:t>R$ 518.822,40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 514.783,06</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/08/2026</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 141,09</x:t>
@@ -846,10 +846,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>6431070.01191805</x:v>
+        <x:v>6431351.20191805</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>6431069.18191805</x:v>
+        <x:v>6431350.37191805</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>0.83</x:v>
@@ -1196,22 +1196,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C21" s="13" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D21" s="13" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E21" s="13" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F21" s="13" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G21" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
@@ -1220,25 +1220,25 @@
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
       <x:c r="A22" s="13" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C22" s="13" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D22" s="13" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E22" s="13" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F22" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G22" s="13" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
@@ -1247,10 +1247,10 @@
     </x:row>
     <x:row r="23" spans="1:11" ht="30" customHeight="1">
       <x:c r="A23" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C23" s="12" t="s">
         <x:v>60</x:v>
@@ -1259,7 +1259,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F23" s="12" t="s">
         <x:v>62</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 18/08/2026, 18:43</x:t>
+    <x:t>Conta: 7983962 | 20/08/2026, 09:49</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>16,0%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.029.884,82</x:t>
+    <x:t>R$ 1.030.784,16</x:t>
   </x:si>
   <x:si>
     <x:t>16,00%|Pós-Fixada</x:t>
@@ -97,7 +97,7 @@
     <x:t>56,1%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 3.605.362,44</x:t>
+    <x:t>R$ 3.608.529,44</x:t>
   </x:si>
   <x:si>
     <x:t>56,00%|Pós-Fixada</x:t>
@@ -118,10 +118,10 @@
     <x:t>R$ 1.603.779,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.604.484,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.604.325,78</x:t>
+    <x:t>R$ 1.605.893,62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.605.418,05</x:t>
   </x:si>
   <x:si>
     <x:t>1.273.885,00</x:t>
@@ -130,16 +130,16 @@
     <x:t>R$ 2.000.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.000.878,21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.680,61</x:t>
+    <x:t>R$ 2.002.635,82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.002.042,76</x:t>
   </x:si>
   <x:si>
     <x:t>27,9%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.796.103,11</x:t>
+    <x:t>R$ 1.796.981,15</x:t>
   </x:si>
   <x:si>
     <x:t>27,90%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -160,10 +160,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>18/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.437,40</x:t>
+    <x:t>19/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.438,19</x:t>
   </x:si>
   <x:si>
     <x:t>15,17</x:t>
@@ -172,10 +172,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 21.805,04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 21.705,37</x:t>
+    <x:t>R$ 21.816,91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 21.714,56</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -187,25 +187,25 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 518.822,40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 514.783,06</x:t>
+    <x:t>R$ 519.092,54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 514.992,42</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,09</x:t>
+    <x:t>R$ 141,16</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.255.475,67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.249.338,16</x:t>
+    <x:t>R$ 1.256.071,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.249.800,08</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,83</x:t>
@@ -846,10 +846,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>6431351.20191805</x:v>
+        <x:v>6436295.58476525</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>6431350.37191805</x:v>
+        <x:v>6436294.75476525</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>0.83</x:v>

--- a/data/positions/Posição Consolidada - 7983962.xlsx
+++ b/data/positions/Posição Consolidada - 7983962.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 7983962 | 20/08/2026, 09:49</x:t>
+    <x:t>Conta: 7983962 | 21/08/2026, 14:52</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>16,0%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.030.784,16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16,00%|Pós-Fixada</x:t>
+    <x:t>19,7%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.031.234,13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,60%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.000.949,68</x:t>
   </x:si>
   <x:si>
-    <x:t>56,1%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.608.529,44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>56,00%|Pós-Fixada</x:t>
+    <x:t>46,0%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.409.230,05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,90%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>17/08/2026</x:t>
@@ -118,31 +118,31 @@
     <x:t>R$ 1.603.779,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.605.893,62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.605.418,05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.273.885,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.002.635,82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.002.042,76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27,9%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.796.981,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27,90%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 1.606.598,79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.605.964,56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>510.333,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 801.223,03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 802.631,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 802.314,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,3%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.798.796,29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -160,10 +160,10 @@
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>19/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.438,19</x:t>
+    <x:t>21/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.439,63</x:t>
   </x:si>
   <x:si>
     <x:t>15,17</x:t>
@@ -172,10 +172,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 21.816,91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 21.714,56</x:t>
+    <x:t>R$ 21.838,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 21.731,50</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -187,28 +187,28 @@
     <x:t>353.356,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 519.092,54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 514.992,42</x:t>
+    <x:t>R$ 519.633,42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 515.411,60</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,16</x:t>
+    <x:t>R$ 141,30</x:t>
   </x:si>
   <x:si>
     <x:t>8.898,52</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.256.071,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.249.800,08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,83</x:t>
+    <x:t>R$ 1.257.324,11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.250.770,71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2,20</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -238,7 +238,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>0,83</x:t>
+    <x:t>2,2</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -846,13 +846,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>6436295.58476525</x:v>
+        <x:v>5239262.66420238</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>6436294.75476525</x:v>
+        <x:v>5239260.46420238</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>0.83</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
